--- a/importEmploy.xlsx
+++ b/importEmploy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\New folder\crmHanhChinhNhanSu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C48573A-6649-4020-8FD6-798617075BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21BD8A7-A3DA-454F-AEBB-14ACFB7A9F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1740" windowWidth="18900" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3600" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
   <si>
     <t>HN</t>
   </si>
@@ -85,49 +85,7 @@
     <t>7000000002</t>
   </si>
   <si>
-    <t>DEP04</t>
-  </si>
-  <si>
-    <t>POS05</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>Nhan Vien 100</t>
-  </si>
-  <si>
-    <t>10/04/2024</t>
-  </si>
-  <si>
-    <t>11/04/1990</t>
-  </si>
-  <si>
-    <t>100000000100</t>
-  </si>
-  <si>
-    <t>11/04/2010</t>
-  </si>
-  <si>
-    <t>Dia chi TT 100</t>
-  </si>
-  <si>
-    <t>Dia chi TTam 100</t>
-  </si>
-  <si>
-    <t>nhanvien100@company.com</t>
-  </si>
-  <si>
-    <t>nhanvien100@gmail.com</t>
-  </si>
-  <si>
-    <t>0900000100</t>
-  </si>
-  <si>
-    <t>0900001100</t>
-  </si>
-  <si>
-    <t>7000000100</t>
   </si>
   <si>
     <t>STT</t>
@@ -1354,6 +1312,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1384,9 +1366,6 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1397,27 +1376,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1722,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ101"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1750,75 +1708,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="6" customFormat="1" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="37"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="42"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="28" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="M1" s="35"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE1" s="44"/>
-      <c r="AF1" s="44"/>
-      <c r="AG1" s="44"/>
-      <c r="AH1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL1" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="AM1" s="4"/>
       <c r="AN1" s="5"/>
@@ -1836,102 +1794,102 @@
       <c r="AZ1" s="5"/>
     </row>
     <row r="2" spans="1:52" s="6" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="P2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="Q2" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="R2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="S2" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="T2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="U2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="V2" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="W2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="X2" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="Y2" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="Z2" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="AA2" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="AB2" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="AC2" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="AD2" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="AE2" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="AF2" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="S2" s="18" t="s">
+      <c r="AG2" s="22" t="s">
         <v>69</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="U2" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="V2" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="W2" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="X2" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y2" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z2" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA2" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB2" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC2" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD2" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE2" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF2" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG2" s="22" t="s">
-        <v>83</v>
       </c>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
@@ -1958,7 +1916,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -2024,7 +1982,7 @@
         <v>4</v>
       </c>
       <c r="X3" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="Y3" s="23">
         <v>45953</v>
@@ -2039,13 +1997,13 @@
         <v>123</v>
       </c>
       <c r="AC3" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="AD3">
         <v>1</v>
       </c>
       <c r="AE3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="AF3" s="23">
         <v>45219</v>
@@ -2054,7 +2012,7 @@
         <v>45585</v>
       </c>
       <c r="AH3" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
@@ -2161,90 +2119,19 @@
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>23</v>
-      </c>
-      <c r="B101" t="s">
-        <v>24</v>
-      </c>
-      <c r="C101" t="s">
-        <v>25</v>
-      </c>
-      <c r="D101" t="s">
-        <v>22</v>
-      </c>
-      <c r="E101" t="s">
-        <v>21</v>
-      </c>
-      <c r="F101" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" t="s">
-        <v>0</v>
-      </c>
-      <c r="I101" t="s">
-        <v>1</v>
-      </c>
-      <c r="J101" t="s">
-        <v>2</v>
-      </c>
-      <c r="K101" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" t="s">
-        <v>27</v>
-      </c>
-      <c r="M101" t="s">
-        <v>28</v>
-      </c>
-      <c r="N101" t="s">
-        <v>0</v>
-      </c>
-      <c r="O101" t="s">
-        <v>29</v>
-      </c>
-      <c r="P101" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q101" t="s">
-        <v>31</v>
-      </c>
-      <c r="R101" t="s">
-        <v>32</v>
-      </c>
-      <c r="S101" t="s">
-        <v>33</v>
-      </c>
-      <c r="T101" t="s">
-        <v>34</v>
-      </c>
-      <c r="U101" t="s">
-        <v>24</v>
-      </c>
-      <c r="V101" t="s">
-        <v>35</v>
-      </c>
-      <c r="W101" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:K1"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:P1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AG1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/importEmploy.xlsx
+++ b/importEmploy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\New folder\crmHanhChinhNhanSu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21BD8A7-A3DA-454F-AEBB-14ACFB7A9F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3A9238-D882-432B-9A84-7D47EB72F773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27720" yWindow="3570" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
   <si>
     <t>HN</t>
   </si>
@@ -58,9 +58,6 @@
     <t>03/01/1990</t>
   </si>
   <si>
-    <t>100000000002</t>
-  </si>
-  <si>
     <t>03/01/2010</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
   </si>
   <si>
     <t>0900000002</t>
-  </si>
-  <si>
-    <t>0900001002</t>
   </si>
   <si>
     <t>7000000002</t>
@@ -1680,7 +1674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1709,16 +1703,16 @@
   <sheetData>
     <row r="1" spans="1:52" s="6" customFormat="1" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38"/>
       <c r="F1" s="39" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G1" s="40"/>
       <c r="H1" s="40"/>
@@ -1726,57 +1720,57 @@
       <c r="J1" s="40"/>
       <c r="K1" s="41"/>
       <c r="L1" s="24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M1" s="42"/>
       <c r="N1" s="43"/>
       <c r="O1" s="44" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P1" s="45"/>
       <c r="Q1" s="32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R1" s="33"/>
       <c r="S1" s="33"/>
       <c r="T1" s="33"/>
       <c r="U1" s="24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V1" s="25"/>
       <c r="W1" s="25"/>
       <c r="X1" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y1" s="27"/>
       <c r="Z1" s="28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA1" s="27"/>
       <c r="AB1" s="29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AC1" s="30"/>
       <c r="AD1" s="31" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE1" s="30"/>
       <c r="AF1" s="30"/>
       <c r="AG1" s="30"/>
       <c r="AH1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AM1" s="4"/>
       <c r="AN1" s="5"/>
@@ -1796,100 +1790,100 @@
     <row r="2" spans="1:52" s="6" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
       <c r="B2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="J2" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="L2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="M2" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="P2" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="Q2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="R2" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="S2" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="S2" s="18" t="s">
+      <c r="U2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="V2" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="W2" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="X2" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="Y2" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="X2" s="19" t="s">
+      <c r="Z2" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="AA2" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="AB2" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="AA2" s="20" t="s">
+      <c r="AC2" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="AB2" s="21" t="s">
+      <c r="AD2" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="AC2" s="21" t="s">
+      <c r="AE2" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="AD2" s="22" t="s">
+      <c r="AF2" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="AE2" s="22" t="s">
+      <c r="AG2" s="22" t="s">
         <v>67</v>
-      </c>
-      <c r="AF2" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="AG2" s="22" t="s">
-        <v>69</v>
       </c>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
@@ -1916,7 +1910,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -1945,44 +1939,44 @@
       <c r="K3" t="s">
         <v>3</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3">
+        <v>100000000002</v>
+      </c>
+      <c r="M3" t="s">
         <v>12</v>
-      </c>
-      <c r="M3" t="s">
-        <v>13</v>
       </c>
       <c r="N3" t="s">
         <v>0</v>
       </c>
       <c r="O3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" t="s">
         <v>14</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>16</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>17</v>
       </c>
-      <c r="S3" t="s">
-        <v>18</v>
-      </c>
-      <c r="T3" t="s">
-        <v>19</v>
+      <c r="T3">
+        <v>900001002</v>
       </c>
       <c r="U3" t="s">
         <v>6</v>
       </c>
       <c r="V3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W3" t="s">
         <v>4</v>
       </c>
       <c r="X3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="Y3" s="23">
         <v>45953</v>
@@ -1997,13 +1991,13 @@
         <v>123</v>
       </c>
       <c r="AC3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AD3">
         <v>1</v>
       </c>
       <c r="AE3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AF3" s="23">
         <v>45219</v>
@@ -2012,111 +2006,7 @@
         <v>45585</v>
       </c>
       <c r="AH3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
-      </c>
-      <c r="H4">
-        <v>7</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>9</v>
-      </c>
-      <c r="K4">
-        <v>10</v>
-      </c>
-      <c r="L4">
-        <v>11</v>
-      </c>
-      <c r="M4">
-        <v>12</v>
-      </c>
-      <c r="N4">
-        <v>13</v>
-      </c>
-      <c r="O4">
-        <v>14</v>
-      </c>
-      <c r="P4">
-        <v>15</v>
-      </c>
-      <c r="Q4">
-        <v>16</v>
-      </c>
-      <c r="R4">
-        <v>17</v>
-      </c>
-      <c r="S4">
-        <v>18</v>
-      </c>
-      <c r="T4">
-        <v>19</v>
-      </c>
-      <c r="U4">
-        <v>20</v>
-      </c>
-      <c r="V4">
-        <v>21</v>
-      </c>
-      <c r="W4">
-        <v>22</v>
-      </c>
-      <c r="X4">
-        <v>23</v>
-      </c>
-      <c r="Y4">
-        <v>24</v>
-      </c>
-      <c r="Z4">
-        <v>25</v>
-      </c>
-      <c r="AA4">
-        <v>26</v>
-      </c>
-      <c r="AB4">
-        <v>27</v>
-      </c>
-      <c r="AC4">
-        <v>28</v>
-      </c>
-      <c r="AD4">
-        <v>29</v>
-      </c>
-      <c r="AE4">
-        <v>30</v>
-      </c>
-      <c r="AF4">
-        <v>31</v>
-      </c>
-      <c r="AG4">
-        <v>32</v>
-      </c>
-      <c r="AH4">
-        <v>33</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
